--- a/artfynd/A 49320-2023 artfynd.xlsx
+++ b/artfynd/A 49320-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125508786</v>
+        <v>125509496</v>
       </c>
       <c r="B2" t="n">
-        <v>78947</v>
+        <v>91459</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>602140</v>
+        <v>602176</v>
       </c>
       <c r="R2" t="n">
-        <v>6930378</v>
+        <v>6930342</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125509496</v>
+        <v>125508786</v>
       </c>
       <c r="B3" t="n">
-        <v>91459</v>
+        <v>78947</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>602176</v>
+        <v>602140</v>
       </c>
       <c r="R3" t="n">
-        <v>6930342</v>
+        <v>6930378</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 49320-2023 artfynd.xlsx
+++ b/artfynd/A 49320-2023 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>125509496</v>
       </c>
       <c r="B2" t="n">
-        <v>91459</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91513</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,12 +785,7 @@
         <v>125508786</v>
       </c>
       <c r="B3" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 49320-2023 artfynd.xlsx
+++ b/artfynd/A 49320-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125509496</v>
       </c>
       <c r="B2" t="n">
-        <v>91513</v>
+        <v>91520</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 49320-2023 artfynd.xlsx
+++ b/artfynd/A 49320-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125509496</v>
       </c>
       <c r="B2" t="n">
-        <v>91520</v>
+        <v>91524</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>125508786</v>
       </c>
       <c r="B3" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 49320-2023 artfynd.xlsx
+++ b/artfynd/A 49320-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125509496</v>
       </c>
       <c r="B2" t="n">
-        <v>91524</v>
+        <v>91528</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>125508786</v>
       </c>
       <c r="B3" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 49320-2023 artfynd.xlsx
+++ b/artfynd/A 49320-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125509496</v>
       </c>
       <c r="B2" t="n">
-        <v>91528</v>
+        <v>91530</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>125508786</v>
       </c>
       <c r="B3" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 49320-2023 artfynd.xlsx
+++ b/artfynd/A 49320-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125509496</v>
       </c>
       <c r="B2" t="n">
-        <v>91530</v>
+        <v>91532</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
